--- a/13. NCU Complete Women's Starring List from 1st June.xlsx
+++ b/13. NCU Complete Women's Starring List from 1st June.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17730" windowHeight="14955" tabRatio="841"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17730" windowHeight="14955" tabRatio="841" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Bangor" sheetId="12" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="North Down" sheetId="33" r:id="rId7"/>
     <sheet name="Waringstown" sheetId="36" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="130">
   <si>
     <t>1st XI</t>
   </si>
@@ -330,21 +330,12 @@
     <t>Oshadi</t>
   </si>
   <si>
-    <t>EVIE</t>
-  </si>
-  <si>
     <t>MAXWELL</t>
   </si>
   <si>
     <t>STACI</t>
   </si>
   <si>
-    <t>JANSE VAN RENSBURG</t>
-  </si>
-  <si>
-    <t>NICOLIEN</t>
-  </si>
-  <si>
     <t>AMY</t>
   </si>
   <si>
@@ -375,15 +366,6 @@
     <t>BECKY</t>
   </si>
   <si>
-    <t>BULLICK</t>
-  </si>
-  <si>
-    <t>ELLIE</t>
-  </si>
-  <si>
-    <t>BOYD</t>
-  </si>
-  <si>
     <t>Pidgeon</t>
   </si>
   <si>
@@ -418,6 +400,27 @@
   </si>
   <si>
     <t>Megan</t>
+  </si>
+  <si>
+    <t>WEBSTER</t>
+  </si>
+  <si>
+    <t>REBECCA</t>
+  </si>
+  <si>
+    <t>MEGAN</t>
+  </si>
+  <si>
+    <t>GOWDY</t>
+  </si>
+  <si>
+    <t>BENSON</t>
+  </si>
+  <si>
+    <t>SIMPSON</t>
+  </si>
+  <si>
+    <t>RACHAEL</t>
   </si>
 </sst>
 </file>
@@ -722,7 +725,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -875,24 +878,9 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1502,7 +1490,7 @@
       <c r="C7" s="48"/>
       <c r="D7" s="48"/>
       <c r="E7" s="36" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="F7" s="37"/>
       <c r="G7" s="37"/>
@@ -1526,7 +1514,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C9" s="43"/>
       <c r="D9" s="43"/>
@@ -1642,12 +1630,12 @@
         <v>4</v>
       </c>
       <c r="B6" s="60" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C6" s="60"/>
       <c r="D6" s="60"/>
       <c r="E6" s="60" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="F6" s="60"/>
       <c r="G6" s="60"/>
@@ -1659,7 +1647,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="60" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C7" s="60"/>
       <c r="D7" s="60"/>
@@ -1976,7 +1964,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="62" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C16" s="42"/>
       <c r="D16" s="42"/>
@@ -2027,12 +2015,12 @@
         <v>7</v>
       </c>
       <c r="B19" s="73" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C19" s="74"/>
       <c r="D19" s="74"/>
       <c r="E19" s="74" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F19" s="74"/>
       <c r="G19" s="74"/>
@@ -2259,12 +2247,12 @@
         <v>7</v>
       </c>
       <c r="B9" s="79" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C9" s="79"/>
       <c r="D9" s="79"/>
       <c r="E9" s="79" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F9" s="79"/>
       <c r="G9" s="79"/>
@@ -2919,120 +2907,120 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="102" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102" t="s">
-        <v>113</v>
-      </c>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="103"/>
+      <c r="B3" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+      <c r="A4" s="35">
         <v>2</v>
       </c>
-      <c r="B4" s="100" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="100"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100" t="s">
-        <v>99</v>
-      </c>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="101"/>
+      <c r="B4" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="100"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="96" t="s">
+      <c r="B5" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="C5" s="96"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96" t="s">
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="63"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="35">
+        <v>4</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="100"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="35">
+        <v>5</v>
+      </c>
+      <c r="B7" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="100"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>6</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="63"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="39">
+        <v>7</v>
+      </c>
+      <c r="B9" s="101" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="101"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="101" t="s">
         <v>101</v>
       </c>
-      <c r="F5" s="96"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="96"/>
-      <c r="I5" s="97"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>4</v>
-      </c>
-      <c r="B6" s="100" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="100"/>
-      <c r="D6" s="100"/>
-      <c r="E6" s="100" t="s">
-        <v>103</v>
-      </c>
-      <c r="F6" s="100"/>
-      <c r="G6" s="100"/>
-      <c r="H6" s="100"/>
-      <c r="I6" s="101"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="100" t="s">
-        <v>114</v>
-      </c>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="100" t="s">
-        <v>115</v>
-      </c>
-      <c r="F7" s="100"/>
-      <c r="G7" s="100"/>
-      <c r="H7" s="100"/>
-      <c r="I7" s="101"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="35">
-        <v>6</v>
-      </c>
-      <c r="B8" s="104" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104" t="s">
-        <v>122</v>
-      </c>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="104"/>
-      <c r="I8" s="105"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10">
-        <v>7</v>
-      </c>
-      <c r="B9" s="98" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9" s="98"/>
-      <c r="D9" s="98"/>
-      <c r="E9" s="98" t="s">
-        <v>104</v>
-      </c>
-      <c r="F9" s="98"/>
-      <c r="G9" s="98"/>
-      <c r="H9" s="98"/>
-      <c r="I9" s="99"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="101"/>
+      <c r="H9" s="101"/>
+      <c r="I9" s="102"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -3101,7 +3089,7 @@
       <c r="C3" s="47"/>
       <c r="D3" s="47"/>
       <c r="E3" s="47" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F3" s="47"/>
       <c r="G3" s="47"/>
@@ -3113,12 +3101,12 @@
         <v>2</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C4" s="42"/>
       <c r="D4" s="42"/>
       <c r="E4" s="42" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F4" s="42"/>
       <c r="G4" s="42"/>
@@ -3130,12 +3118,12 @@
         <v>3</v>
       </c>
       <c r="B5" s="66" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C5" s="66"/>
       <c r="D5" s="66"/>
       <c r="E5" s="66" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F5" s="66"/>
       <c r="G5" s="66"/>
@@ -3152,7 +3140,7 @@
       <c r="C6" s="42"/>
       <c r="D6" s="42"/>
       <c r="E6" s="42" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F6" s="42"/>
       <c r="G6" s="42"/>
@@ -3169,7 +3157,7 @@
       <c r="C7" s="42"/>
       <c r="D7" s="42"/>
       <c r="E7" s="42" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F7" s="42"/>
       <c r="G7" s="42"/>
@@ -3197,18 +3185,18 @@
       <c r="A9" s="10">
         <v>7</v>
       </c>
-      <c r="B9" s="106" t="s">
+      <c r="B9" s="103" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="106"/>
-      <c r="D9" s="106"/>
-      <c r="E9" s="106" t="s">
-        <v>125</v>
-      </c>
-      <c r="F9" s="106"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="106"/>
-      <c r="I9" s="107"/>
+      <c r="C9" s="103"/>
+      <c r="D9" s="103"/>
+      <c r="E9" s="103" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" s="103"/>
+      <c r="G9" s="103"/>
+      <c r="H9" s="103"/>
+      <c r="I9" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="17">

--- a/13. NCU Complete Women's Starring List from 1st June.xlsx
+++ b/13. NCU Complete Women's Starring List from 1st June.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17730" windowHeight="14955" tabRatio="841" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17730" windowHeight="14955" tabRatio="841" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Bangor" sheetId="12" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="North Down" sheetId="33" r:id="rId7"/>
     <sheet name="Waringstown" sheetId="36" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="162913" calcOnSave="0"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="131">
   <si>
     <t>1st XI</t>
   </si>
@@ -108,9 +108,6 @@
     <t>Morrow</t>
   </si>
   <si>
-    <t>McCollum</t>
-  </si>
-  <si>
     <t>Mitchell</t>
   </si>
   <si>
@@ -390,9 +387,6 @@
     <t>Aimee</t>
   </si>
   <si>
-    <t>Susie</t>
-  </si>
-  <si>
     <t>Cupitt</t>
   </si>
   <si>
@@ -421,6 +415,15 @@
   </si>
   <si>
     <t>RACHAEL</t>
+  </si>
+  <si>
+    <t>Caulfield</t>
+  </si>
+  <si>
+    <t>Amy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rachael </t>
   </si>
 </sst>
 </file>
@@ -725,7 +728,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -775,13 +778,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -796,27 +792,13 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -826,25 +808,62 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -862,29 +881,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1438,7 +1444,7 @@
       <c r="C3" s="47"/>
       <c r="D3" s="47"/>
       <c r="E3" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1451,7 +1457,7 @@
       <c r="C4" s="42"/>
       <c r="D4" s="42"/>
       <c r="E4" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1459,12 +1465,12 @@
         <v>3</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="42"/>
       <c r="D5" s="42"/>
       <c r="E5" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1477,7 +1483,7 @@
       <c r="C6" s="42"/>
       <c r="D6" s="42"/>
       <c r="E6" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1485,12 +1491,12 @@
         <v>5</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="48"/>
       <c r="D7" s="48"/>
       <c r="E7" s="36" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F7" s="37"/>
       <c r="G7" s="37"/>
@@ -1501,12 +1507,12 @@
         <v>6</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="42"/>
       <c r="D8" s="42"/>
       <c r="E8" s="26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1514,12 +1520,12 @@
         <v>7</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C9" s="43"/>
       <c r="D9" s="43"/>
       <c r="E9" s="27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1547,30 +1553,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
       <c r="H1" s="12"/>
       <c r="I1" s="8"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="28"/>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53" t="s">
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
       <c r="H2" s="29"/>
       <c r="I2" s="30"/>
     </row>
@@ -1578,123 +1584,130 @@
       <c r="A3" s="31">
         <v>1</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="55"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="61"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="32">
         <v>2</v>
       </c>
-      <c r="B4" s="49" t="s">
+      <c r="B4" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="50"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="56"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="32">
         <v>3</v>
       </c>
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="57"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="50"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="32">
         <v>4</v>
       </c>
-      <c r="B6" s="60" t="s">
+      <c r="B6" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60" t="s">
-        <v>112</v>
-      </c>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="61"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="54"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="32">
         <v>5</v>
       </c>
-      <c r="B7" s="60" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="61"/>
+      <c r="B7" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="54"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="32">
         <v>6</v>
       </c>
-      <c r="B8" s="56" t="s">
+      <c r="B8" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="57"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="50"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>7</v>
       </c>
-      <c r="B9" s="58" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58" t="s">
-        <v>69</v>
-      </c>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="59"/>
+      <c r="B9" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:I3"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="E8:I8"/>
     <mergeCell ref="B9:D9"/>
@@ -1705,13 +1718,6 @@
     <mergeCell ref="E6:I6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="E7:I7"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1754,120 +1760,120 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="76" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="65"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="77"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2</v>
       </c>
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="65" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="42"/>
       <c r="D4" s="42"/>
       <c r="E4" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F4" s="42"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
-      <c r="I4" s="63"/>
+      <c r="I4" s="66"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>3</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" s="42"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F5" s="42"/>
       <c r="G5" s="42"/>
       <c r="H5" s="42"/>
-      <c r="I5" s="63"/>
+      <c r="I5" s="66"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>4</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" s="42"/>
       <c r="D6" s="42"/>
       <c r="E6" s="42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F6" s="42"/>
       <c r="G6" s="42"/>
       <c r="H6" s="42"/>
-      <c r="I6" s="63"/>
+      <c r="I6" s="66"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>5</v>
       </c>
-      <c r="B7" s="66" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="67"/>
+      <c r="B7" s="70" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="70"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="71"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>6</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" s="42"/>
       <c r="D8" s="42"/>
       <c r="E8" s="42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F8" s="42"/>
       <c r="G8" s="42"/>
       <c r="H8" s="42"/>
-      <c r="I8" s="63"/>
+      <c r="I8" s="66"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>7</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="42"/>
       <c r="D9" s="42"/>
       <c r="E9" s="42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F9" s="42"/>
       <c r="G9" s="42"/>
       <c r="H9" s="42"/>
-      <c r="I9" s="63"/>
+      <c r="I9" s="66"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="22"/>
@@ -1895,16 +1901,16 @@
     </row>
     <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
-      <c r="B12" s="69" t="s">
+      <c r="B12" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="69"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69" t="s">
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
       <c r="H12" s="34"/>
       <c r="I12" s="9"/>
     </row>
@@ -1912,24 +1918,24 @@
       <c r="A13" s="6">
         <v>1</v>
       </c>
-      <c r="B13" s="70" t="s">
+      <c r="B13" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="72"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="75"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>2</v>
       </c>
-      <c r="B14" s="62" t="s">
+      <c r="B14" s="65" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="42"/>
@@ -1940,135 +1946,145 @@
       <c r="F14" s="42"/>
       <c r="G14" s="42"/>
       <c r="H14" s="42"/>
-      <c r="I14" s="63"/>
+      <c r="I14" s="66"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>3</v>
       </c>
-      <c r="B15" s="62" t="s">
-        <v>42</v>
+      <c r="B15" s="65" t="s">
+        <v>41</v>
       </c>
       <c r="C15" s="42"/>
       <c r="D15" s="42"/>
       <c r="E15" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F15" s="42"/>
       <c r="G15" s="42"/>
       <c r="H15" s="42"/>
-      <c r="I15" s="63"/>
+      <c r="I15" s="66"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>4</v>
       </c>
-      <c r="B16" s="62" t="s">
-        <v>120</v>
+      <c r="B16" s="65" t="s">
+        <v>118</v>
       </c>
       <c r="C16" s="42"/>
       <c r="D16" s="42"/>
       <c r="E16" s="42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F16" s="42"/>
       <c r="G16" s="42"/>
       <c r="H16" s="42"/>
-      <c r="I16" s="63"/>
+      <c r="I16" s="66"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>5</v>
       </c>
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="66"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="66" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" s="66"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="66"/>
-      <c r="I17" s="67"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="71"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>6</v>
       </c>
-      <c r="B18" s="62" t="s">
-        <v>57</v>
+      <c r="B18" s="65" t="s">
+        <v>56</v>
       </c>
       <c r="C18" s="42"/>
       <c r="D18" s="42"/>
       <c r="E18" s="42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F18" s="42"/>
       <c r="G18" s="42"/>
       <c r="H18" s="42"/>
-      <c r="I18" s="63"/>
+      <c r="I18" s="66"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>7</v>
       </c>
-      <c r="B19" s="73" t="s">
+      <c r="B19" s="62" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63" t="s">
         <v>114</v>
       </c>
-      <c r="C19" s="74"/>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74" t="s">
-        <v>115</v>
-      </c>
-      <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="75"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="64"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>8</v>
       </c>
-      <c r="B20" s="62" t="s">
-        <v>60</v>
+      <c r="B20" s="65" t="s">
+        <v>59</v>
       </c>
       <c r="C20" s="42"/>
       <c r="D20" s="42"/>
       <c r="E20" s="42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F20" s="42"/>
       <c r="G20" s="42"/>
       <c r="H20" s="42"/>
-      <c r="I20" s="63"/>
+      <c r="I20" s="66"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
         <v>9</v>
       </c>
-      <c r="B21" s="76" t="s">
-        <v>62</v>
+      <c r="B21" s="67" t="s">
+        <v>61</v>
       </c>
       <c r="C21" s="43"/>
       <c r="D21" s="43"/>
       <c r="E21" s="43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F21" s="43"/>
       <c r="G21" s="43"/>
       <c r="H21" s="43"/>
-      <c r="I21" s="77"/>
+      <c r="I21" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:I19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:I20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:I21"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:I18"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="E3:I3"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:I5"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:I6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E7:I7"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="E8:I8"/>
     <mergeCell ref="B16:D16"/>
@@ -2085,22 +2101,12 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:I13"/>
     <mergeCell ref="E14:I14"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:I18"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="E3:I3"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:I5"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:I6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:I7"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:I19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:I20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:I21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2150,46 +2156,46 @@
       <c r="C3" s="47"/>
       <c r="D3" s="47"/>
       <c r="E3" s="47" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F3" s="47"/>
       <c r="G3" s="47"/>
       <c r="H3" s="47"/>
-      <c r="I3" s="78"/>
+      <c r="I3" s="80"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C4" s="42"/>
       <c r="D4" s="42"/>
       <c r="E4" s="42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F4" s="42"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
-      <c r="I4" s="63"/>
+      <c r="I4" s="66"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="66" t="s">
+      <c r="B5" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="67"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="71"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
@@ -2201,66 +2207,73 @@
       <c r="C6" s="42"/>
       <c r="D6" s="42"/>
       <c r="E6" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F6" s="42"/>
       <c r="G6" s="42"/>
       <c r="H6" s="42"/>
-      <c r="I6" s="63"/>
+      <c r="I6" s="66"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>5</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" s="42"/>
       <c r="D7" s="42"/>
       <c r="E7" s="42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F7" s="42"/>
       <c r="G7" s="42"/>
       <c r="H7" s="42"/>
-      <c r="I7" s="63"/>
+      <c r="I7" s="66"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>6</v>
       </c>
-      <c r="B8" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="66"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="67"/>
+      <c r="B8" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="71"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <v>7</v>
       </c>
-      <c r="B9" s="79" t="s">
+      <c r="B9" s="78" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="78"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="78" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79" t="s">
-        <v>118</v>
-      </c>
-      <c r="F9" s="79"/>
-      <c r="G9" s="79"/>
-      <c r="H9" s="79"/>
-      <c r="I9" s="80"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="78"/>
+      <c r="I9" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:I3"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="E8:I8"/>
     <mergeCell ref="B9:D9"/>
@@ -2271,13 +2284,6 @@
     <mergeCell ref="E6:I6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="E7:I7"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2326,12 +2332,12 @@
       <c r="C3" s="47"/>
       <c r="D3" s="47"/>
       <c r="E3" s="47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F3" s="47"/>
       <c r="G3" s="47"/>
       <c r="H3" s="47"/>
-      <c r="I3" s="78"/>
+      <c r="I3" s="80"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
@@ -2343,29 +2349,29 @@
       <c r="C4" s="42"/>
       <c r="D4" s="42"/>
       <c r="E4" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F4" s="42"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
-      <c r="I4" s="63"/>
+      <c r="I4" s="66"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="66" t="s">
+      <c r="B5" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66" t="s">
-        <v>75</v>
-      </c>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="67"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="71"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
@@ -2377,12 +2383,12 @@
       <c r="C6" s="42"/>
       <c r="D6" s="42"/>
       <c r="E6" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F6" s="42"/>
       <c r="G6" s="42"/>
       <c r="H6" s="42"/>
-      <c r="I6" s="63"/>
+      <c r="I6" s="66"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
@@ -2394,46 +2400,46 @@
       <c r="C7" s="42"/>
       <c r="D7" s="42"/>
       <c r="E7" s="42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F7" s="42"/>
       <c r="G7" s="42"/>
       <c r="H7" s="42"/>
-      <c r="I7" s="63"/>
+      <c r="I7" s="66"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="41">
         <v>6</v>
       </c>
-      <c r="B8" s="81" t="s">
+      <c r="B8" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="85"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="85" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="81"/>
-      <c r="D8" s="81"/>
-      <c r="E8" s="81" t="s">
-        <v>78</v>
-      </c>
-      <c r="F8" s="81"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="81"/>
-      <c r="I8" s="82"/>
+      <c r="F8" s="85"/>
+      <c r="G8" s="85"/>
+      <c r="H8" s="85"/>
+      <c r="I8" s="86"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="41">
         <v>7</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81" t="s">
-        <v>79</v>
-      </c>
-      <c r="F9" s="81"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="82"/>
+      <c r="C9" s="85"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="85" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="85"/>
+      <c r="G9" s="85"/>
+      <c r="H9" s="85"/>
+      <c r="I9" s="86"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="22"/>
@@ -2484,12 +2490,12 @@
       <c r="C13" s="47"/>
       <c r="D13" s="47"/>
       <c r="E13" s="47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" s="47"/>
       <c r="G13" s="47"/>
       <c r="H13" s="47"/>
-      <c r="I13" s="78"/>
+      <c r="I13" s="80"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
@@ -2501,41 +2507,41 @@
       <c r="C14" s="42"/>
       <c r="D14" s="42"/>
       <c r="E14" s="42" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F14" s="42"/>
       <c r="G14" s="42"/>
       <c r="H14" s="42"/>
-      <c r="I14" s="63"/>
+      <c r="I14" s="66"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="41">
         <v>3</v>
       </c>
-      <c r="B15" s="81" t="s">
+      <c r="B15" s="85" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="85"/>
+      <c r="D15" s="85"/>
+      <c r="E15" s="85" t="s">
         <v>81</v>
       </c>
-      <c r="C15" s="81"/>
-      <c r="D15" s="81"/>
-      <c r="E15" s="81" t="s">
-        <v>82</v>
-      </c>
-      <c r="F15" s="81"/>
-      <c r="G15" s="81"/>
-      <c r="H15" s="81"/>
-      <c r="I15" s="82"/>
+      <c r="F15" s="85"/>
+      <c r="G15" s="85"/>
+      <c r="H15" s="85"/>
+      <c r="I15" s="86"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="41">
         <v>4</v>
       </c>
       <c r="B16" s="83" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C16" s="83"/>
       <c r="D16" s="83"/>
       <c r="E16" s="83" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F16" s="83"/>
       <c r="G16" s="83"/>
@@ -2552,12 +2558,12 @@
       <c r="C17" s="42"/>
       <c r="D17" s="42"/>
       <c r="E17" s="42" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F17" s="42"/>
       <c r="G17" s="42"/>
       <c r="H17" s="42"/>
-      <c r="I17" s="63"/>
+      <c r="I17" s="66"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="41">
@@ -2569,7 +2575,7 @@
       <c r="C18" s="83"/>
       <c r="D18" s="83"/>
       <c r="E18" s="83" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F18" s="83"/>
       <c r="G18" s="83"/>
@@ -2580,55 +2586,83 @@
       <c r="A19" s="7">
         <v>7</v>
       </c>
-      <c r="B19" s="66" t="s">
+      <c r="B19" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" s="66"/>
-      <c r="G19" s="66"/>
-      <c r="H19" s="66"/>
-      <c r="I19" s="67"/>
+      <c r="C19" s="70"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="71"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>8</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C20" s="42"/>
       <c r="D20" s="42"/>
       <c r="E20" s="42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F20" s="42"/>
       <c r="G20" s="42"/>
       <c r="H20" s="42"/>
-      <c r="I20" s="63"/>
+      <c r="I20" s="66"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="40">
         <v>9</v>
       </c>
-      <c r="B21" s="85" t="s">
+      <c r="B21" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="81"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="81" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="85"/>
-      <c r="D21" s="85"/>
-      <c r="E21" s="85" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" s="85"/>
-      <c r="G21" s="85"/>
-      <c r="H21" s="85"/>
-      <c r="I21" s="86"/>
+      <c r="F21" s="81"/>
+      <c r="G21" s="81"/>
+      <c r="H21" s="81"/>
+      <c r="I21" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:I3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:I5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:I6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E7:I7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E8:I8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:I9"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:I13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:I14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:I15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:I16"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:I20"/>
     <mergeCell ref="B21:D21"/>
@@ -2639,34 +2673,6 @@
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="E19:I19"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:I14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:I15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:I16"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E13:I13"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:I7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:I8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:I9"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:I5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:I6"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2678,30 +2684,30 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="91"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="95"/>
       <c r="H1" s="19"/>
       <c r="I1" s="13"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92" t="s">
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
       <c r="H2" s="18"/>
       <c r="I2" s="14"/>
     </row>
@@ -2709,120 +2715,120 @@
       <c r="A3" s="16">
         <v>1</v>
       </c>
-      <c r="B3" s="94" t="s">
+      <c r="B3" s="98" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94" t="s">
-        <v>88</v>
-      </c>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="95"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="99"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
         <v>2</v>
       </c>
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="91" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="91"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="91" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="87"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="87" t="s">
-        <v>90</v>
-      </c>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="88"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="92"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
         <v>3</v>
       </c>
-      <c r="B5" s="96" t="s">
+      <c r="B5" s="87" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87" t="s">
         <v>91</v>
       </c>
-      <c r="C5" s="96"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96" t="s">
-        <v>92</v>
-      </c>
-      <c r="F5" s="96"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="96"/>
-      <c r="I5" s="97"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="88"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="17">
         <v>4</v>
       </c>
-      <c r="B6" s="87" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="87"/>
-      <c r="D6" s="87"/>
-      <c r="E6" s="87" t="s">
-        <v>86</v>
-      </c>
-      <c r="F6" s="87"/>
-      <c r="G6" s="87"/>
-      <c r="H6" s="87"/>
-      <c r="I6" s="88"/>
+      <c r="B6" s="91" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="91"/>
+      <c r="D6" s="91"/>
+      <c r="E6" s="91" t="s">
+        <v>85</v>
+      </c>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="92"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="17">
         <v>5</v>
       </c>
-      <c r="B7" s="87" t="s">
+      <c r="B7" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="87"/>
-      <c r="D7" s="87"/>
-      <c r="E7" s="87" t="s">
-        <v>94</v>
-      </c>
-      <c r="F7" s="87"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="88"/>
+      <c r="C7" s="91"/>
+      <c r="D7" s="91"/>
+      <c r="E7" s="91" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" s="91"/>
+      <c r="G7" s="91"/>
+      <c r="H7" s="91"/>
+      <c r="I7" s="92"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>6</v>
       </c>
-      <c r="B8" s="96" t="s">
+      <c r="B8" s="87" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96" t="s">
-        <v>96</v>
-      </c>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="97"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="87"/>
+      <c r="H8" s="87"/>
+      <c r="I8" s="88"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="21">
         <v>7</v>
       </c>
-      <c r="B9" s="98" t="s">
+      <c r="B9" s="89" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="89"/>
+      <c r="D9" s="89"/>
+      <c r="E9" s="89" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="98"/>
-      <c r="D9" s="98"/>
-      <c r="E9" s="98" t="s">
-        <v>98</v>
-      </c>
-      <c r="F9" s="98"/>
-      <c r="G9" s="98"/>
-      <c r="H9" s="98"/>
-      <c r="I9" s="99"/>
+      <c r="F9" s="89"/>
+      <c r="G9" s="89"/>
+      <c r="H9" s="89"/>
+      <c r="I9" s="90"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
@@ -2848,6 +2854,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:I3"/>
     <mergeCell ref="E8:I8"/>
     <mergeCell ref="E9:I9"/>
     <mergeCell ref="B8:D8"/>
@@ -2858,13 +2871,6 @@
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="E7:I7"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2908,85 +2914,85 @@
         <v>1</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C3" s="47"/>
       <c r="D3" s="47"/>
       <c r="E3" s="47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F3" s="47"/>
       <c r="G3" s="47"/>
       <c r="H3" s="47"/>
-      <c r="I3" s="78"/>
+      <c r="I3" s="80"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="35">
         <v>2</v>
       </c>
       <c r="B4" s="48" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
       <c r="E4" s="48" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F4" s="48"/>
       <c r="G4" s="48"/>
       <c r="H4" s="48"/>
-      <c r="I4" s="100"/>
+      <c r="I4" s="102"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>3</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C5" s="42"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F5" s="42"/>
       <c r="G5" s="42"/>
       <c r="H5" s="42"/>
-      <c r="I5" s="63"/>
+      <c r="I5" s="66"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="35">
         <v>4</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C6" s="48"/>
       <c r="D6" s="48"/>
       <c r="E6" s="48" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F6" s="48"/>
       <c r="G6" s="48"/>
       <c r="H6" s="48"/>
-      <c r="I6" s="100"/>
+      <c r="I6" s="102"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="35">
         <v>5</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C7" s="48"/>
       <c r="D7" s="48"/>
       <c r="E7" s="48" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F7" s="48"/>
       <c r="G7" s="48"/>
       <c r="H7" s="48"/>
-      <c r="I7" s="100"/>
+      <c r="I7" s="102"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
@@ -2998,32 +3004,39 @@
       <c r="C8" s="42"/>
       <c r="D8" s="42"/>
       <c r="E8" s="42" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F8" s="42"/>
       <c r="G8" s="42"/>
       <c r="H8" s="42"/>
-      <c r="I8" s="63"/>
+      <c r="I8" s="66"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <v>7</v>
       </c>
-      <c r="B9" s="101" t="s">
-        <v>127</v>
-      </c>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101" t="s">
-        <v>101</v>
-      </c>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
-      <c r="H9" s="101"/>
-      <c r="I9" s="102"/>
+      <c r="B9" s="100" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="100"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" s="100"/>
+      <c r="G9" s="100"/>
+      <c r="H9" s="100"/>
+      <c r="I9" s="101"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:I3"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="E8:I8"/>
     <mergeCell ref="B9:D9"/>
@@ -3034,13 +3047,6 @@
     <mergeCell ref="E6:I6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="E7:I7"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3048,10 +3054,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
@@ -3064,7 +3070,7 @@
       <c r="H1" s="11"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="46" t="s">
         <v>1</v>
@@ -3079,75 +3085,75 @@
       <c r="H2" s="4"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>1</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="47"/>
       <c r="D3" s="47"/>
       <c r="E3" s="47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F3" s="47"/>
       <c r="G3" s="47"/>
       <c r="H3" s="47"/>
-      <c r="I3" s="78"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I3" s="80"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="42"/>
       <c r="D4" s="42"/>
       <c r="E4" s="42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F4" s="42"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
-      <c r="I4" s="63"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I4" s="66"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="66" t="s">
+      <c r="B5" s="70" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70" t="s">
         <v>105</v>
       </c>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66" t="s">
-        <v>106</v>
-      </c>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="67"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="71"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>4</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C6" s="42"/>
       <c r="D6" s="42"/>
       <c r="E6" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F6" s="42"/>
       <c r="G6" s="42"/>
       <c r="H6" s="42"/>
-      <c r="I6" s="63"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I6" s="66"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>5</v>
       </c>
@@ -3157,59 +3163,50 @@
       <c r="C7" s="42"/>
       <c r="D7" s="42"/>
       <c r="E7" s="42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F7" s="42"/>
       <c r="G7" s="42"/>
       <c r="H7" s="42"/>
-      <c r="I7" s="63"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="I7" s="66"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="41">
         <v>6</v>
       </c>
-      <c r="B8" s="66" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="66"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66" t="s">
-        <v>78</v>
-      </c>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="67"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10">
+      <c r="B8" s="85" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="85"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="85" t="s">
+        <v>129</v>
+      </c>
+      <c r="F8" s="85"/>
+      <c r="G8" s="85"/>
+      <c r="H8" s="85"/>
+      <c r="I8" s="86"/>
+    </row>
+    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="40">
         <v>7</v>
       </c>
       <c r="B9" s="103" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C9" s="103"/>
       <c r="D9" s="103"/>
       <c r="E9" s="103" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="F9" s="103"/>
       <c r="G9" s="103"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="104"/>
+      <c r="H9" s="104"/>
+      <c r="I9" s="105"/>
+      <c r="K9" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:I8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:I5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:I6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:I7"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="E4:I4"/>
     <mergeCell ref="A1:G1"/>
@@ -3217,7 +3214,18 @@
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="E3:I3"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E8:I8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:I5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:I6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E7:I7"/>
+    <mergeCell ref="E9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/13. NCU Complete Women's Starring List from 1st June.xlsx
+++ b/13. NCU Complete Women's Starring List from 1st June.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="130">
   <si>
     <t>1st XI</t>
   </si>
@@ -421,9 +421,6 @@
   </si>
   <si>
     <t>Amy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rachael </t>
   </si>
 </sst>
 </file>
@@ -771,6 +768,12 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -778,6 +781,13 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -792,13 +802,27 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -808,45 +832,41 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -864,33 +884,10 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1415,34 +1412,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
       <c r="E3" s="25" t="s">
         <v>27</v>
       </c>
@@ -1451,11 +1448,11 @@
       <c r="A4" s="7">
         <v>2</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
       <c r="E4" s="26" t="s">
         <v>28</v>
       </c>
@@ -1464,11 +1461,11 @@
       <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
       <c r="E5" s="26" t="s">
         <v>28</v>
       </c>
@@ -1477,11 +1474,11 @@
       <c r="A6" s="7">
         <v>4</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
       <c r="E6" s="26" t="s">
         <v>30</v>
       </c>
@@ -1493,8 +1490,8 @@
       <c r="B7" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
       <c r="E7" s="36" t="s">
         <v>120</v>
       </c>
@@ -1506,11 +1503,11 @@
       <c r="A8" s="7">
         <v>6</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
       <c r="E8" s="26" t="s">
         <v>33</v>
       </c>
@@ -1519,11 +1516,11 @@
       <c r="A9" s="10">
         <v>7</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
       <c r="E9" s="27" t="s">
         <v>30</v>
       </c>
@@ -1553,30 +1550,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
       <c r="H1" s="12"/>
       <c r="I1" s="8"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="28"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59" t="s">
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
       <c r="H2" s="29"/>
       <c r="I2" s="30"/>
     </row>
@@ -1584,130 +1581,123 @@
       <c r="A3" s="31">
         <v>1</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="B3" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60" t="s">
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="61"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="57"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="32">
         <v>2</v>
       </c>
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55" t="s">
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="56"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="52"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="32">
         <v>3</v>
       </c>
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49" t="s">
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="50"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="59"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="32">
         <v>4</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="62" t="s">
         <v>110</v>
       </c>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53" t="s">
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62" t="s">
         <v>111</v>
       </c>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="54"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="63"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="32">
         <v>5</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="B7" s="62" t="s">
         <v>112</v>
       </c>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53" t="s">
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="54"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="63"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="32">
         <v>6</v>
       </c>
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49" t="s">
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="50"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="59"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>7</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51" t="s">
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="52"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:I3"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="E8:I8"/>
     <mergeCell ref="B9:D9"/>
@@ -1718,6 +1708,13 @@
     <mergeCell ref="E6:I6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="E7:I7"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1729,30 +1726,30 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="11"/>
       <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
       <c r="H2" s="4"/>
       <c r="I2" s="5"/>
     </row>
@@ -1760,120 +1757,120 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76" t="s">
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="77"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="67"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2</v>
       </c>
-      <c r="B4" s="65" t="s">
+      <c r="B4" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42" t="s">
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="66"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="65"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42" t="s">
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="66"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="65"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>4</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42" t="s">
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="66"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="65"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>5</v>
       </c>
-      <c r="B7" s="70" t="s">
+      <c r="B7" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70" t="s">
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="71"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="69"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>6</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42" t="s">
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="66"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="65"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>7</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42" t="s">
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="66"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="65"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="22"/>
@@ -1887,30 +1884,30 @@
       <c r="I10" s="24"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
       <c r="H11" s="11"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
-      <c r="B12" s="72" t="s">
+      <c r="B12" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72" t="s">
+      <c r="C12" s="71"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
       <c r="H12" s="34"/>
       <c r="I12" s="9"/>
     </row>
@@ -1918,157 +1915,179 @@
       <c r="A13" s="6">
         <v>1</v>
       </c>
-      <c r="B13" s="73" t="s">
+      <c r="B13" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74" t="s">
+      <c r="C13" s="73"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="75"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="74"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>2</v>
       </c>
-      <c r="B14" s="65" t="s">
+      <c r="B14" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42" t="s">
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="66"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="65"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>3</v>
       </c>
-      <c r="B15" s="65" t="s">
+      <c r="B15" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42" t="s">
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="66"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="65"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>4</v>
       </c>
-      <c r="B16" s="65" t="s">
+      <c r="B16" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42" t="s">
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="66"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="65"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>5</v>
       </c>
-      <c r="B17" s="69" t="s">
+      <c r="B17" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="70"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70" t="s">
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="70"/>
-      <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
-      <c r="I17" s="71"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="69"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>6</v>
       </c>
-      <c r="B18" s="65" t="s">
+      <c r="B18" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42" t="s">
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="66"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="65"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>7</v>
       </c>
-      <c r="B19" s="62" t="s">
+      <c r="B19" s="75" t="s">
         <v>113</v>
       </c>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63" t="s">
+      <c r="C19" s="76"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="76" t="s">
         <v>114</v>
       </c>
-      <c r="F19" s="63"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="64"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="76"/>
+      <c r="I19" s="77"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>8</v>
       </c>
-      <c r="B20" s="65" t="s">
+      <c r="B20" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42" t="s">
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="66"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="65"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
         <v>9</v>
       </c>
-      <c r="B21" s="67" t="s">
+      <c r="B21" s="78" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43" t="s">
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="68"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:I19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:I20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:I21"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E8:I8"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:I16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:I9"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:I15"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E13:I13"/>
+    <mergeCell ref="E14:I14"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="A1:G1"/>
@@ -2085,28 +2104,6 @@
     <mergeCell ref="E6:I6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="E7:I7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:I8"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:I16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:I9"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:I15"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="E13:I13"/>
-    <mergeCell ref="E14:I14"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:I19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:I20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:I21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2119,30 +2116,30 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="11"/>
       <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
       <c r="H2" s="4"/>
       <c r="I2" s="5"/>
     </row>
@@ -2150,130 +2147,123 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47" t="s">
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
       <c r="I3" s="80"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42" t="s">
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="66"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="65"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70" t="s">
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="71"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="69"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>4</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42" t="s">
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="66"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="65"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>5</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42" t="s">
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="66"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="65"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>6</v>
       </c>
-      <c r="B8" s="70" t="s">
+      <c r="B8" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70" t="s">
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="71"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="69"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <v>7</v>
       </c>
-      <c r="B9" s="78" t="s">
+      <c r="B9" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="78"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78" t="s">
+      <c r="C9" s="81"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81" t="s">
         <v>117</v>
       </c>
-      <c r="F9" s="78"/>
-      <c r="G9" s="78"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="79"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:I3"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="E8:I8"/>
     <mergeCell ref="B9:D9"/>
@@ -2284,6 +2274,13 @@
     <mergeCell ref="E6:I6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="E7:I7"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2295,30 +2292,30 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="11"/>
       <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
       <c r="H2" s="4"/>
       <c r="I2" s="5"/>
     </row>
@@ -2326,120 +2323,120 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47" t="s">
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
       <c r="I3" s="80"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42" t="s">
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="66"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="65"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70" t="s">
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="71"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="69"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>4</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42" t="s">
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="66"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="65"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>5</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42" t="s">
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="66"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="65"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="41">
         <v>6</v>
       </c>
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="83" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="85"/>
-      <c r="D8" s="85"/>
-      <c r="E8" s="85" t="s">
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83" t="s">
         <v>77</v>
       </c>
-      <c r="F8" s="85"/>
-      <c r="G8" s="85"/>
-      <c r="H8" s="85"/>
-      <c r="I8" s="86"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="84"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="41">
         <v>7</v>
       </c>
-      <c r="B9" s="85" t="s">
+      <c r="B9" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="85"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85" t="s">
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83" t="s">
         <v>78</v>
       </c>
-      <c r="F9" s="85"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="85"/>
-      <c r="I9" s="86"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="84"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="22"/>
@@ -2453,30 +2450,30 @@
       <c r="I10" s="24"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
       <c r="H11" s="11"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46" t="s">
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
       <c r="H12" s="4"/>
       <c r="I12" s="5"/>
     </row>
@@ -2484,185 +2481,157 @@
       <c r="A13" s="6">
         <v>1</v>
       </c>
-      <c r="B13" s="47" t="s">
+      <c r="B13" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47" t="s">
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
       <c r="I13" s="80"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>2</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42" t="s">
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="66"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="65"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="41">
         <v>3</v>
       </c>
-      <c r="B15" s="85" t="s">
+      <c r="B15" s="83" t="s">
         <v>80</v>
       </c>
-      <c r="C15" s="85"/>
-      <c r="D15" s="85"/>
-      <c r="E15" s="85" t="s">
+      <c r="C15" s="83"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="83" t="s">
         <v>81</v>
       </c>
-      <c r="F15" s="85"/>
-      <c r="G15" s="85"/>
-      <c r="H15" s="85"/>
-      <c r="I15" s="86"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="83"/>
+      <c r="I15" s="84"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="41">
         <v>4</v>
       </c>
-      <c r="B16" s="83" t="s">
+      <c r="B16" s="85" t="s">
         <v>82</v>
       </c>
-      <c r="C16" s="83"/>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83" t="s">
+      <c r="C16" s="85"/>
+      <c r="D16" s="85"/>
+      <c r="E16" s="85" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="83"/>
-      <c r="G16" s="83"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="84"/>
+      <c r="F16" s="85"/>
+      <c r="G16" s="85"/>
+      <c r="H16" s="85"/>
+      <c r="I16" s="86"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>5</v>
       </c>
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42" t="s">
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="66"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="65"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="41">
         <v>6</v>
       </c>
-      <c r="B18" s="83" t="s">
+      <c r="B18" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="83"/>
-      <c r="D18" s="83"/>
-      <c r="E18" s="83" t="s">
+      <c r="C18" s="85"/>
+      <c r="D18" s="85"/>
+      <c r="E18" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="F18" s="83"/>
-      <c r="G18" s="83"/>
-      <c r="H18" s="83"/>
-      <c r="I18" s="84"/>
+      <c r="F18" s="85"/>
+      <c r="G18" s="85"/>
+      <c r="H18" s="85"/>
+      <c r="I18" s="86"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>7</v>
       </c>
-      <c r="B19" s="70" t="s">
+      <c r="B19" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="70"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70" t="s">
+      <c r="C19" s="68"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="70"/>
-      <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="71"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="69"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>8</v>
       </c>
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42" t="s">
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="66"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="65"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="40">
         <v>9</v>
       </c>
-      <c r="B21" s="81" t="s">
+      <c r="B21" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="81"/>
-      <c r="D21" s="81"/>
-      <c r="E21" s="81" t="s">
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87" t="s">
         <v>85</v>
       </c>
-      <c r="F21" s="81"/>
-      <c r="G21" s="81"/>
-      <c r="H21" s="81"/>
-      <c r="I21" s="82"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="87"/>
+      <c r="H21" s="87"/>
+      <c r="I21" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:I3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:I5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:I6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:I7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:I8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:I9"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E13:I13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:I14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:I15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:I16"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:I20"/>
     <mergeCell ref="B21:D21"/>
@@ -2673,6 +2642,34 @@
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="E19:I19"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:I14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:I15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:I16"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:I13"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E7:I7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E8:I8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:I9"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:I5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:I6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2684,30 +2681,30 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="95"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="93"/>
       <c r="H1" s="19"/>
       <c r="I1" s="13"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
-      <c r="B2" s="96" t="s">
+      <c r="B2" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96" t="s">
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
       <c r="H2" s="18"/>
       <c r="I2" s="14"/>
     </row>
@@ -2715,120 +2712,120 @@
       <c r="A3" s="16">
         <v>1</v>
       </c>
-      <c r="B3" s="98" t="s">
+      <c r="B3" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98" t="s">
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96" t="s">
         <v>87</v>
       </c>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="99"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="97"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
         <v>2</v>
       </c>
-      <c r="B4" s="91" t="s">
+      <c r="B4" s="89" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="91"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="91" t="s">
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89" t="s">
         <v>89</v>
       </c>
-      <c r="F4" s="91"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="92"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="90"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
         <v>3</v>
       </c>
-      <c r="B5" s="87" t="s">
+      <c r="B5" s="98" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="87"/>
-      <c r="D5" s="87"/>
-      <c r="E5" s="87" t="s">
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98" t="s">
         <v>91</v>
       </c>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="88"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="99"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="17">
         <v>4</v>
       </c>
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="89" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="91"/>
-      <c r="D6" s="91"/>
-      <c r="E6" s="91" t="s">
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="91"/>
-      <c r="G6" s="91"/>
-      <c r="H6" s="91"/>
-      <c r="I6" s="92"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="90"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="17">
         <v>5</v>
       </c>
-      <c r="B7" s="91" t="s">
+      <c r="B7" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="91"/>
-      <c r="D7" s="91"/>
-      <c r="E7" s="91" t="s">
+      <c r="C7" s="89"/>
+      <c r="D7" s="89"/>
+      <c r="E7" s="89" t="s">
         <v>93</v>
       </c>
-      <c r="F7" s="91"/>
-      <c r="G7" s="91"/>
-      <c r="H7" s="91"/>
-      <c r="I7" s="92"/>
+      <c r="F7" s="89"/>
+      <c r="G7" s="89"/>
+      <c r="H7" s="89"/>
+      <c r="I7" s="90"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>6</v>
       </c>
-      <c r="B8" s="87" t="s">
+      <c r="B8" s="98" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="87"/>
-      <c r="D8" s="87"/>
-      <c r="E8" s="87" t="s">
+      <c r="C8" s="98"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="98" t="s">
         <v>95</v>
       </c>
-      <c r="F8" s="87"/>
-      <c r="G8" s="87"/>
-      <c r="H8" s="87"/>
-      <c r="I8" s="88"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="99"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="21">
         <v>7</v>
       </c>
-      <c r="B9" s="89" t="s">
+      <c r="B9" s="100" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="89"/>
-      <c r="D9" s="89"/>
-      <c r="E9" s="89" t="s">
+      <c r="C9" s="100"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100" t="s">
         <v>97</v>
       </c>
-      <c r="F9" s="89"/>
-      <c r="G9" s="89"/>
-      <c r="H9" s="89"/>
-      <c r="I9" s="90"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="100"/>
+      <c r="H9" s="100"/>
+      <c r="I9" s="101"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
@@ -2854,13 +2851,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:I3"/>
     <mergeCell ref="E8:I8"/>
     <mergeCell ref="E9:I9"/>
     <mergeCell ref="B8:D8"/>
@@ -2871,6 +2861,13 @@
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="E7:I7"/>
     <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2882,30 +2879,30 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="11"/>
       <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
       <c r="H2" s="4"/>
       <c r="I2" s="5"/>
     </row>
@@ -2913,130 +2910,123 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47" t="s">
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49" t="s">
         <v>109</v>
       </c>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
       <c r="I3" s="80"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="35">
         <v>2</v>
       </c>
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48" t="s">
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
       <c r="I4" s="102"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42" t="s">
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="66"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="65"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="35">
         <v>4</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48" t="s">
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="50"/>
       <c r="I6" s="102"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="35">
         <v>5</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48" t="s">
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
       <c r="I7" s="102"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>6</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42" t="s">
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="66"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="65"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <v>7</v>
       </c>
-      <c r="B9" s="100" t="s">
+      <c r="B9" s="103" t="s">
         <v>125</v>
       </c>
-      <c r="C9" s="100"/>
-      <c r="D9" s="100"/>
-      <c r="E9" s="100" t="s">
+      <c r="C9" s="103"/>
+      <c r="D9" s="103"/>
+      <c r="E9" s="103" t="s">
         <v>100</v>
       </c>
-      <c r="F9" s="100"/>
-      <c r="G9" s="100"/>
-      <c r="H9" s="100"/>
-      <c r="I9" s="101"/>
+      <c r="F9" s="103"/>
+      <c r="G9" s="103"/>
+      <c r="H9" s="103"/>
+      <c r="I9" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:I3"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="E8:I8"/>
     <mergeCell ref="B9:D9"/>
@@ -3047,6 +3037,13 @@
     <mergeCell ref="E6:I6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="E7:I7"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3058,30 +3055,30 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="11"/>
       <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
       <c r="H2" s="4"/>
       <c r="I2" s="5"/>
     </row>
@@ -3089,131 +3086,124 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47" t="s">
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
       <c r="I3" s="80"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42" t="s">
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="66"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="65"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70" t="s">
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="71"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="69"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>4</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42" t="s">
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="66"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="65"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>5</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42" t="s">
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="66"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="65"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="41">
         <v>6</v>
       </c>
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="83" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="85"/>
-      <c r="D8" s="85"/>
-      <c r="E8" s="85" t="s">
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83" t="s">
         <v>129</v>
       </c>
-      <c r="F8" s="85"/>
-      <c r="G8" s="85"/>
-      <c r="H8" s="85"/>
-      <c r="I8" s="86"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="84"/>
     </row>
     <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="40">
         <v>7</v>
       </c>
-      <c r="B9" s="103" t="s">
+      <c r="B9" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="103"/>
-      <c r="D9" s="103"/>
-      <c r="E9" s="103" t="s">
-        <v>130</v>
-      </c>
-      <c r="F9" s="103"/>
-      <c r="G9" s="103"/>
-      <c r="H9" s="104"/>
-      <c r="I9" s="105"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="43"/>
       <c r="K9" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:I3"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="E8:I8"/>
     <mergeCell ref="B9:D9"/>
@@ -3224,6 +3214,13 @@
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="E7:I7"/>
     <mergeCell ref="E9:G9"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/13. NCU Complete Women's Starring List from 1st June.xlsx
+++ b/13. NCU Complete Women's Starring List from 1st June.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17730" windowHeight="14955" tabRatio="841" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17730" windowHeight="14955" tabRatio="841" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Bangor" sheetId="12" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="131">
   <si>
     <t>1st XI</t>
   </si>
@@ -51,9 +51,6 @@
     <t>Thomas</t>
   </si>
   <si>
-    <t>Cunningham</t>
-  </si>
-  <si>
     <t>Watt</t>
   </si>
   <si>
@@ -174,9 +171,6 @@
     <t>Lara</t>
   </si>
   <si>
-    <t>McCay</t>
-  </si>
-  <si>
     <t>McNaught</t>
   </si>
   <si>
@@ -421,6 +415,15 @@
   </si>
   <si>
     <t>Amy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cunningham </t>
+  </si>
+  <si>
+    <t>Tillie</t>
+  </si>
+  <si>
+    <t>Katie</t>
   </si>
 </sst>
 </file>
@@ -479,7 +482,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -512,18 +515,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8EFA00"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -654,15 +651,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -725,7 +713,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -756,7 +744,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
@@ -766,12 +754,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -781,13 +769,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -802,55 +783,62 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -868,28 +856,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1436,12 +1428,12 @@
         <v>1</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="49"/>
       <c r="D3" s="49"/>
       <c r="E3" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1449,12 +1441,12 @@
         <v>2</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="44"/>
       <c r="D4" s="44"/>
       <c r="E4" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1462,12 +1454,12 @@
         <v>3</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" s="44"/>
       <c r="D5" s="44"/>
       <c r="E5" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1475,12 +1467,12 @@
         <v>4</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" s="44"/>
       <c r="D6" s="44"/>
       <c r="E6" s="26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1488,12 +1480,12 @@
         <v>5</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" s="50"/>
       <c r="D7" s="50"/>
       <c r="E7" s="36" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F7" s="37"/>
       <c r="G7" s="37"/>
@@ -1504,12 +1496,12 @@
         <v>6</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" s="44"/>
       <c r="D8" s="44"/>
       <c r="E8" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1517,12 +1509,12 @@
         <v>7</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C9" s="45"/>
       <c r="D9" s="45"/>
       <c r="E9" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1550,30 +1542,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="12"/>
       <c r="I1" s="8"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="28"/>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55" t="s">
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
       <c r="H2" s="29"/>
       <c r="I2" s="30"/>
     </row>
@@ -1581,123 +1573,130 @@
       <c r="A3" s="31">
         <v>1</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="62" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="57"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="63"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="32">
         <v>2</v>
       </c>
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="52"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="58"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="32">
         <v>3</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="59"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="52"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="32">
         <v>4</v>
       </c>
-      <c r="B6" s="62" t="s">
-        <v>110</v>
-      </c>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62" t="s">
-        <v>111</v>
-      </c>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="63"/>
+      <c r="B6" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="56"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="32">
         <v>5</v>
       </c>
-      <c r="B7" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62" t="s">
-        <v>68</v>
-      </c>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="63"/>
+      <c r="B7" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="56"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="32">
         <v>6</v>
       </c>
-      <c r="B8" s="58" t="s">
+      <c r="B8" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="59"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="52"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>7</v>
       </c>
-      <c r="B9" s="60" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="61"/>
+      <c r="B9" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:I3"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="E8:I8"/>
     <mergeCell ref="B9:D9"/>
@@ -1708,13 +1707,6 @@
     <mergeCell ref="E6:I6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="E7:I7"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1757,47 +1749,47 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="66" t="s">
+      <c r="B3" s="70" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="67"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="71"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+      <c r="A4" s="41">
         <v>2</v>
       </c>
-      <c r="B4" s="64" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="65"/>
+      <c r="B4" s="104" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="78"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>3</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="44"/>
       <c r="D5" s="44"/>
       <c r="E5" s="44" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F5" s="44"/>
       <c r="G5" s="44"/>
@@ -1809,12 +1801,12 @@
         <v>4</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="44"/>
       <c r="D6" s="44"/>
       <c r="E6" s="44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
@@ -1822,55 +1814,55 @@
       <c r="I6" s="65"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="41">
         <v>5</v>
       </c>
-      <c r="B7" s="68" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="69"/>
+      <c r="B7" s="105" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="79" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="79"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="80"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>6</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C8" s="44"/>
       <c r="D8" s="44"/>
       <c r="E8" s="44" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F8" s="44"/>
       <c r="G8" s="44"/>
       <c r="H8" s="44"/>
       <c r="I8" s="65"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
         <v>7</v>
       </c>
-      <c r="B9" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="65"/>
+      <c r="B9" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="67"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="22"/>
@@ -1897,17 +1889,17 @@
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="71" t="s">
+      <c r="A12" s="102"/>
+      <c r="B12" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71" t="s">
+      <c r="C12" s="103"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="103"/>
       <c r="H12" s="34"/>
       <c r="I12" s="9"/>
     </row>
@@ -1915,47 +1907,47 @@
       <c r="A13" s="6">
         <v>1</v>
       </c>
-      <c r="B13" s="72" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13" s="73"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
+      <c r="B13" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
       <c r="I13" s="74"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="A14" s="41">
         <v>2</v>
       </c>
-      <c r="B14" s="64" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="65"/>
+      <c r="B14" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" s="107"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="107" t="s">
+        <v>129</v>
+      </c>
+      <c r="F14" s="107"/>
+      <c r="G14" s="107"/>
+      <c r="H14" s="107"/>
+      <c r="I14" s="108"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>3</v>
       </c>
       <c r="B15" s="64" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" s="44"/>
       <c r="D15" s="44"/>
       <c r="E15" s="44" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F15" s="44"/>
       <c r="G15" s="44"/>
@@ -1967,12 +1959,12 @@
         <v>4</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C16" s="44"/>
       <c r="D16" s="44"/>
       <c r="E16" s="44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F16" s="44"/>
       <c r="G16" s="44"/>
@@ -1980,33 +1972,33 @@
       <c r="I16" s="65"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="A17" s="41">
         <v>5</v>
       </c>
-      <c r="B17" s="70" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="68"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="68"/>
-      <c r="I17" s="69"/>
+      <c r="B17" s="109" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="F17" s="50"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="50"/>
+      <c r="I17" s="96"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>6</v>
       </c>
       <c r="B18" s="64" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C18" s="44"/>
       <c r="D18" s="44"/>
       <c r="E18" s="44" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F18" s="44"/>
       <c r="G18" s="44"/>
@@ -2014,33 +2006,33 @@
       <c r="I18" s="65"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
+      <c r="A19" s="98">
         <v>7</v>
       </c>
-      <c r="B19" s="75" t="s">
-        <v>113</v>
-      </c>
-      <c r="C19" s="76"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="76" t="s">
-        <v>114</v>
-      </c>
-      <c r="F19" s="76"/>
-      <c r="G19" s="76"/>
-      <c r="H19" s="76"/>
-      <c r="I19" s="77"/>
+      <c r="B19" s="99" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="100"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="100" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" s="100"/>
+      <c r="G19" s="100"/>
+      <c r="H19" s="100"/>
+      <c r="I19" s="101"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>8</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C20" s="44"/>
       <c r="D20" s="44"/>
       <c r="E20" s="44" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F20" s="44"/>
       <c r="G20" s="44"/>
@@ -2051,27 +2043,37 @@
       <c r="A21" s="10">
         <v>9</v>
       </c>
-      <c r="B21" s="78" t="s">
-        <v>61</v>
+      <c r="B21" s="66" t="s">
+        <v>59</v>
       </c>
       <c r="C21" s="45"/>
       <c r="D21" s="45"/>
       <c r="E21" s="45" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F21" s="45"/>
       <c r="G21" s="45"/>
       <c r="H21" s="45"/>
-      <c r="I21" s="79"/>
+      <c r="I21" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:I19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:I20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:I21"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:I18"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="E3:I3"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:I5"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:I6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E7:I7"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="E8:I8"/>
     <mergeCell ref="B16:D16"/>
@@ -2088,22 +2090,12 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:I13"/>
     <mergeCell ref="E14:I14"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:I18"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="E3:I3"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:I5"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:I6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:I7"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:I19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:I20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:I21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2148,29 +2140,29 @@
         <v>1</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="49"/>
       <c r="D3" s="49"/>
       <c r="E3" s="49" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F3" s="49"/>
       <c r="G3" s="49"/>
       <c r="H3" s="49"/>
-      <c r="I3" s="80"/>
+      <c r="I3" s="74"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C4" s="44"/>
       <c r="D4" s="44"/>
       <c r="E4" s="44" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
@@ -2182,12 +2174,12 @@
         <v>3</v>
       </c>
       <c r="B5" s="68" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C5" s="68"/>
       <c r="D5" s="68"/>
       <c r="E5" s="68" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F5" s="68"/>
       <c r="G5" s="68"/>
@@ -2204,7 +2196,7 @@
       <c r="C6" s="44"/>
       <c r="D6" s="44"/>
       <c r="E6" s="44" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
@@ -2216,12 +2208,12 @@
         <v>5</v>
       </c>
       <c r="B7" s="44" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C7" s="44"/>
       <c r="D7" s="44"/>
       <c r="E7" s="44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
@@ -2233,12 +2225,12 @@
         <v>6</v>
       </c>
       <c r="B8" s="68" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" s="68"/>
       <c r="D8" s="68"/>
       <c r="E8" s="68" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8" s="68"/>
       <c r="G8" s="68"/>
@@ -2249,21 +2241,28 @@
       <c r="A9" s="39">
         <v>7</v>
       </c>
-      <c r="B9" s="81" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81" t="s">
-        <v>117</v>
-      </c>
-      <c r="F9" s="81"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="82"/>
+      <c r="B9" s="72" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72" t="s">
+        <v>115</v>
+      </c>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:I3"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="E8:I8"/>
     <mergeCell ref="B9:D9"/>
@@ -2274,13 +2273,6 @@
     <mergeCell ref="E6:I6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="E7:I7"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2329,24 +2321,24 @@
       <c r="C3" s="49"/>
       <c r="D3" s="49"/>
       <c r="E3" s="49" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F3" s="49"/>
       <c r="G3" s="49"/>
       <c r="H3" s="49"/>
-      <c r="I3" s="80"/>
+      <c r="I3" s="74"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" s="44"/>
       <c r="D4" s="44"/>
       <c r="E4" s="44" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
@@ -2358,12 +2350,12 @@
         <v>3</v>
       </c>
       <c r="B5" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C5" s="68"/>
       <c r="D5" s="68"/>
       <c r="E5" s="68" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F5" s="68"/>
       <c r="G5" s="68"/>
@@ -2375,12 +2367,12 @@
         <v>4</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="44"/>
       <c r="D6" s="44"/>
       <c r="E6" s="44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
@@ -2392,12 +2384,12 @@
         <v>5</v>
       </c>
       <c r="B7" s="44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="44"/>
       <c r="D7" s="44"/>
       <c r="E7" s="44" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
@@ -2408,35 +2400,35 @@
       <c r="A8" s="41">
         <v>6</v>
       </c>
-      <c r="B8" s="83" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="84"/>
+      <c r="B8" s="79" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="79"/>
+      <c r="D8" s="79"/>
+      <c r="E8" s="79" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="79"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="80"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="41">
         <v>7</v>
       </c>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="84"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="79" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" s="79"/>
+      <c r="G9" s="79"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="80"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="22"/>
@@ -2482,29 +2474,29 @@
         <v>1</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" s="49"/>
       <c r="D13" s="49"/>
       <c r="E13" s="49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F13" s="49"/>
       <c r="G13" s="49"/>
       <c r="H13" s="49"/>
-      <c r="I13" s="80"/>
+      <c r="I13" s="74"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>2</v>
       </c>
       <c r="B14" s="44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" s="44"/>
       <c r="D14" s="44"/>
       <c r="E14" s="44" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F14" s="44"/>
       <c r="G14" s="44"/>
@@ -2515,47 +2507,47 @@
       <c r="A15" s="41">
         <v>3</v>
       </c>
-      <c r="B15" s="83" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83" t="s">
-        <v>81</v>
-      </c>
-      <c r="F15" s="83"/>
-      <c r="G15" s="83"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="84"/>
+      <c r="B15" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="79"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="79" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="79"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="79"/>
+      <c r="I15" s="80"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="41">
         <v>4</v>
       </c>
-      <c r="B16" s="85" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" s="85"/>
-      <c r="D16" s="85"/>
-      <c r="E16" s="85" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="85"/>
-      <c r="G16" s="85"/>
-      <c r="H16" s="85"/>
-      <c r="I16" s="86"/>
+      <c r="B16" s="77" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="77"/>
+      <c r="D16" s="77"/>
+      <c r="E16" s="77" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="77"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="78"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>5</v>
       </c>
       <c r="B17" s="44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" s="44"/>
       <c r="D17" s="44"/>
       <c r="E17" s="44" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F17" s="44"/>
       <c r="G17" s="44"/>
@@ -2566,30 +2558,30 @@
       <c r="A18" s="41">
         <v>6</v>
       </c>
-      <c r="B18" s="85" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="85"/>
-      <c r="D18" s="85"/>
-      <c r="E18" s="85" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" s="85"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="85"/>
-      <c r="I18" s="86"/>
+      <c r="B18" s="77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="77"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="77" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="77"/>
+      <c r="G18" s="77"/>
+      <c r="H18" s="77"/>
+      <c r="I18" s="78"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>7</v>
       </c>
       <c r="B19" s="68" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19" s="68"/>
       <c r="D19" s="68"/>
       <c r="E19" s="68" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F19" s="68"/>
       <c r="G19" s="68"/>
@@ -2601,12 +2593,12 @@
         <v>8</v>
       </c>
       <c r="B20" s="44" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C20" s="44"/>
       <c r="D20" s="44"/>
       <c r="E20" s="44" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F20" s="44"/>
       <c r="G20" s="44"/>
@@ -2617,21 +2609,49 @@
       <c r="A21" s="40">
         <v>9</v>
       </c>
-      <c r="B21" s="87" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="87"/>
-      <c r="D21" s="87"/>
-      <c r="E21" s="87" t="s">
-        <v>85</v>
-      </c>
-      <c r="F21" s="87"/>
-      <c r="G21" s="87"/>
-      <c r="H21" s="87"/>
-      <c r="I21" s="88"/>
+      <c r="B21" s="75" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="75"/>
+      <c r="D21" s="75"/>
+      <c r="E21" s="75" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" s="75"/>
+      <c r="G21" s="75"/>
+      <c r="H21" s="75"/>
+      <c r="I21" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:I3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:I5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:I6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E7:I7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E8:I8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:I9"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:I13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:I14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:I15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:I16"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:I20"/>
     <mergeCell ref="B21:D21"/>
@@ -2642,34 +2662,6 @@
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="E19:I19"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:I14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:I15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:I16"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E13:I13"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:I7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:I8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:I9"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:I5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:I6"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2681,30 +2673,30 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="93"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="89"/>
       <c r="H1" s="19"/>
       <c r="I1" s="13"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
-      <c r="B2" s="94" t="s">
+      <c r="B2" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94" t="s">
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
       <c r="H2" s="18"/>
       <c r="I2" s="14"/>
     </row>
@@ -2712,120 +2704,120 @@
       <c r="A3" s="16">
         <v>1</v>
       </c>
-      <c r="B3" s="96" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="96" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3" s="96"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="96"/>
-      <c r="I3" s="97"/>
+      <c r="B3" s="92" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="93"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
         <v>2</v>
       </c>
-      <c r="B4" s="89" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89" t="s">
-        <v>89</v>
-      </c>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="90"/>
+      <c r="B4" s="85" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="86"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
         <v>3</v>
       </c>
-      <c r="B5" s="98" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="98"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="98" t="s">
-        <v>91</v>
-      </c>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="99"/>
+      <c r="B5" s="81" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="82"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="17">
         <v>4</v>
       </c>
-      <c r="B6" s="89" t="s">
-        <v>92</v>
-      </c>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="90"/>
+      <c r="B6" s="85" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="85"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="85"/>
+      <c r="G6" s="85"/>
+      <c r="H6" s="85"/>
+      <c r="I6" s="86"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="17">
         <v>5</v>
       </c>
-      <c r="B7" s="89" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="89"/>
-      <c r="D7" s="89"/>
-      <c r="E7" s="89" t="s">
-        <v>93</v>
-      </c>
-      <c r="F7" s="89"/>
-      <c r="G7" s="89"/>
-      <c r="H7" s="89"/>
-      <c r="I7" s="90"/>
+      <c r="B7" s="85" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85" t="s">
+        <v>91</v>
+      </c>
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="86"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>6</v>
       </c>
-      <c r="B8" s="98" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" s="98"/>
-      <c r="D8" s="98"/>
-      <c r="E8" s="98" t="s">
-        <v>95</v>
-      </c>
-      <c r="F8" s="98"/>
-      <c r="G8" s="98"/>
-      <c r="H8" s="98"/>
-      <c r="I8" s="99"/>
+      <c r="B8" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="81"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="81" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="82"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="21">
         <v>7</v>
       </c>
-      <c r="B9" s="100" t="s">
-        <v>96</v>
-      </c>
-      <c r="C9" s="100"/>
-      <c r="D9" s="100"/>
-      <c r="E9" s="100" t="s">
-        <v>97</v>
-      </c>
-      <c r="F9" s="100"/>
-      <c r="G9" s="100"/>
-      <c r="H9" s="100"/>
-      <c r="I9" s="101"/>
+      <c r="B9" s="83" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="84"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
@@ -2851,6 +2843,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:I3"/>
     <mergeCell ref="E8:I8"/>
     <mergeCell ref="E9:I9"/>
     <mergeCell ref="B8:D8"/>
@@ -2861,13 +2860,6 @@
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="E7:I7"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2911,46 +2903,46 @@
         <v>1</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C3" s="49"/>
       <c r="D3" s="49"/>
       <c r="E3" s="49" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F3" s="49"/>
       <c r="G3" s="49"/>
       <c r="H3" s="49"/>
-      <c r="I3" s="80"/>
+      <c r="I3" s="74"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="35">
         <v>2</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C4" s="50"/>
       <c r="D4" s="50"/>
       <c r="E4" s="50" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F4" s="50"/>
       <c r="G4" s="50"/>
       <c r="H4" s="50"/>
-      <c r="I4" s="102"/>
+      <c r="I4" s="96"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>3</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C5" s="44"/>
       <c r="D5" s="44"/>
       <c r="E5" s="44" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F5" s="44"/>
       <c r="G5" s="44"/>
@@ -2962,46 +2954,46 @@
         <v>4</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C6" s="50"/>
       <c r="D6" s="50"/>
       <c r="E6" s="50" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F6" s="50"/>
       <c r="G6" s="50"/>
       <c r="H6" s="50"/>
-      <c r="I6" s="102"/>
+      <c r="I6" s="96"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="35">
         <v>5</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C7" s="50"/>
       <c r="D7" s="50"/>
       <c r="E7" s="50" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F7" s="50"/>
       <c r="G7" s="50"/>
       <c r="H7" s="50"/>
-      <c r="I7" s="102"/>
+      <c r="I7" s="96"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>6</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="44"/>
       <c r="D8" s="44"/>
       <c r="E8" s="44" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F8" s="44"/>
       <c r="G8" s="44"/>
@@ -3012,21 +3004,28 @@
       <c r="A9" s="39">
         <v>7</v>
       </c>
-      <c r="B9" s="103" t="s">
-        <v>125</v>
-      </c>
-      <c r="C9" s="103"/>
-      <c r="D9" s="103"/>
-      <c r="E9" s="103" t="s">
-        <v>100</v>
-      </c>
-      <c r="F9" s="103"/>
-      <c r="G9" s="103"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="104"/>
+      <c r="B9" s="94" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="94"/>
+      <c r="D9" s="94"/>
+      <c r="E9" s="94" t="s">
+        <v>98</v>
+      </c>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:I3"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="E8:I8"/>
     <mergeCell ref="B9:D9"/>
@@ -3037,13 +3036,6 @@
     <mergeCell ref="E6:I6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="E7:I7"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3087,29 +3079,29 @@
         <v>1</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="49"/>
       <c r="D3" s="49"/>
       <c r="E3" s="49" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F3" s="49"/>
       <c r="G3" s="49"/>
       <c r="H3" s="49"/>
-      <c r="I3" s="80"/>
+      <c r="I3" s="74"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C4" s="44"/>
       <c r="D4" s="44"/>
       <c r="E4" s="44" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
@@ -3121,12 +3113,12 @@
         <v>3</v>
       </c>
       <c r="B5" s="68" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C5" s="68"/>
       <c r="D5" s="68"/>
       <c r="E5" s="68" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F5" s="68"/>
       <c r="G5" s="68"/>
@@ -3138,12 +3130,12 @@
         <v>4</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C6" s="44"/>
       <c r="D6" s="44"/>
       <c r="E6" s="44" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
@@ -3155,12 +3147,12 @@
         <v>5</v>
       </c>
       <c r="B7" s="44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="44"/>
       <c r="D7" s="44"/>
       <c r="E7" s="44" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
@@ -3171,39 +3163,46 @@
       <c r="A8" s="41">
         <v>6</v>
       </c>
-      <c r="B8" s="83" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83" t="s">
-        <v>129</v>
-      </c>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="84"/>
+      <c r="B8" s="79" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" s="79"/>
+      <c r="D8" s="79"/>
+      <c r="E8" s="79" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" s="79"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="80"/>
     </row>
     <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="40">
         <v>7</v>
       </c>
-      <c r="B9" s="105" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="105"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="105" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="105"/>
-      <c r="G9" s="105"/>
+      <c r="B9" s="97" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="97"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="97" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="97"/>
+      <c r="G9" s="97"/>
       <c r="H9" s="42"/>
       <c r="I9" s="43"/>
       <c r="K9" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:I3"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="E8:I8"/>
     <mergeCell ref="B9:D9"/>
@@ -3214,13 +3213,6 @@
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="E7:I7"/>
     <mergeCell ref="E9:G9"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
